--- a/mario/ops/cvxlab_models/Split_sut_com/model_settings.xlsx
+++ b/mario/ops/cvxlab_models/Split_sut_com/model_settings.xlsx
@@ -1843,7 +1843,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minimize(sum(entropy(M_pn,M0_pn))+sum(entropy(Y_pn,Y0_pn)))</t>
+          <t>Minimize(sum(entropy(M_pn,M0_pn))+sum(entropy_signed(Y_pn,Y0_pn)))</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yold_p_r&lt;=(I_c_from_to_p@I_com_p_pn@Y_pn_r)*(1+eps)</t>
+          <t>Yold_p_r-absval(Yold_p_r)*eps&lt;=(I_c_from_to_p@I_com_p_pn@Y_pn_r)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yold_p_r&gt;=(I_c_from_to_p@I_com_p_pn@Y_pn_r)*(1-eps)</t>
+          <t>Yold_p_r+absval(Yold_p_r)*eps&gt;=(I_c_from_to_p@I_com_p_pn@Y_pn_r)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
